--- a/Results/MIROCALS_vs_MND_MIROCALS.xlsx
+++ b/Results/MIROCALS_vs_MND_MIROCALS.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>MIROCALS</t>
+          <t>MIROCALS PLACEBO</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>MND MIROCALS</t>
+          <t>MIROCALS MND</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>58.35 ± 10.28</t>
+          <t>58.64 ± 10.53</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4388</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.71 ± 4.94</t>
+          <t>10.09 ± 5.14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,7 +519,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>84 (38.4%)</t>
+          <t>43 (39.4%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>135 (61.6%)</t>
+          <t>66 (60.6%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -582,7 +582,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.0834</v>
+        <v>0.1762</v>
       </c>
     </row>
     <row r="8">
@@ -598,7 +598,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>45 (20.5%)</t>
+          <t>23 (21.1%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>174 (79.5%)</t>
+          <t>86 (78.9%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
